--- a/data/fokito/asistencia/asistencia_fokito.xlsx
+++ b/data/fokito/asistencia/asistencia_fokito.xlsx
@@ -14,10 +14,10 @@
     <sheet name="JM_Sección 1_Seminario" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="MB_Sección 1_Seminario" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="NV_Sección 1_Seminario" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GM_Sección 2_Laboratorio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="JCS_Sección 2_Laboratorio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="VB_Sección 2_Laboratorio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="XX_Sección 2_Laboratorio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="EG_Sección 2_Laboratorio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GM_Sección 2_Laboratorio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="JCS_Sección 2_Laboratorio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="VB_Sección 2_Laboratorio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="JM_Sección 2_Seminario" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="NV_Sección 2_Seminario" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="RM_Sección 2_Seminario" sheetId="14" state="visible" r:id="rId14"/>
@@ -25,16 +25,16 @@
     <sheet name="EG_Sección 3_Laboratorio" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="JM_Sección 3_Laboratorio" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="MB_Sección 3_Laboratorio" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="EG_Sección 3_Seminario" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="JM_Sección 3_Seminario" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="NV_Sección 3_Seminario" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="JM_Sección 3_Seminario" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="NV_Sección 3_Seminario" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="RM_Sección 3_Seminario" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="CC_Sección 4_Laboratorio" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="EG_Sección 4_Laboratorio" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="SM_Sección 4_Laboratorio" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="XX_Sección 4_Laboratorio" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="RM_Sección 4_Seminario" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="SM_Sección 4_Seminario" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="XX_Sección 4_Seminario" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="GF_Sección 4_Laboratorio" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="SM_Sección 4_Laboratorio" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="EG_Sección 4_Seminario" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="GF_Sección 4_Seminario" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="SM_Sección 4_Seminario" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'GM_Sección 1_Laboratorio'!$1:$5</definedName>
@@ -44,10 +44,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'JM_Sección 1_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'MB_Sección 1_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'NV_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'GM_Sección 2_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'JCS_Sección 2_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'VB_Sección 2_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'XX_Sección 2_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'EG_Sección 2_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'GM_Sección 2_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'JCS_Sección 2_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'VB_Sección 2_Laboratorio'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'JM_Sección 2_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'NV_Sección 2_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'RM_Sección 2_Seminario'!$1:$5</definedName>
@@ -55,16 +55,16 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'EG_Sección 3_Laboratorio'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="16">'JM_Sección 3_Laboratorio'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="17">'MB_Sección 3_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'EG_Sección 3_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'JM_Sección 3_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'NV_Sección 3_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'JM_Sección 3_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'NV_Sección 3_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'RM_Sección 3_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="21">'CC_Sección 4_Laboratorio'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="22">'EG_Sección 4_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'SM_Sección 4_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'XX_Sección 4_Laboratorio'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="25">'RM_Sección 4_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="26">'SM_Sección 4_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="27">'XX_Sección 4_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'GF_Sección 4_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'SM_Sección 4_Laboratorio'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'EG_Sección 4_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="26">'GF_Sección 4_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="27">'SM_Sección 4_Seminario'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,7 +815,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: VB</t>
+          <t>Profesor: JCS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1067,7 +1067,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: VB</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1294,7 +1294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1503,7 +1503,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Mondaca Rivera, José Ignacio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1522,6 +1522,556 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Alvarado Salamanca, Matilda Alicia</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ambiado Urrejola, Nicolas Ignacio</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Antivil Lepe, Laura Monserrat</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Araya Trujillo, Magdalena Paz</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Candia Villagra, Valentina Paz</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cerda Ojeda, Josefa Catalina</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Contreras Villarreal, Martina Fernanda</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Jiménez, Florencia Sofía</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Escalona González, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>González Quiñones, Maite Isabel</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Guajardo García, Sofía</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Guzmán Vásquez, Ignacia Mariana</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hernández Elgueta, Sofía Andrea</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Marambio Piutrín, Ignacia Verónica</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Hott, Constanza Sofía</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Murillo Silva, Camila Alejandra</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Navarrete Valenzuela, Christian Antonio</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Parra Urriola, Josefa Catalina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Torres González, María Ignacia</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Ulloa Iturriaga, Javier Ignacio</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vallejos Puentes, Antonia Paz</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Villalobos Poma, Fabián Ignacio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Zorrilla Soto, Manuel Eduardo</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1534,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1743,7 +2293,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Salas Galaz, Juan Carlos</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1762,6 +2312,556 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Varas Carrasco, Nathalie Gabriela</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Acuña Romero, Constanza Annais</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Álvarez Fernández, Eimy Constanza</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Avila Acevedo, Yalitza Xiomara</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Bavestrello Cornejo, Catalina Antonella</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Carrillo Cáceres, Josefina Constanza</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Claros Rodríguez, Isabel Canela</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Colihuinca Castro, Paulina Constanza</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contreras Candia, Benjamín Eduardo</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Cuevas Valdés, Javier Andrés</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Flores Cea, Alison Anaís</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Guzmán Escobar, Elisabeth Alejandra</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Ibarra Guzmán, Ignacia Andrea</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Marincovic Jiménez, Florencia Isabel</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Martinez Clavel, Sofia Valentina</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Maturana Parra, Antonella Constanza</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Sotelo, Constanza Danae</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Nieto Nieto, Erick David</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Oliva Verdugo, María Fernanda</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Romero Martínez, Martina del Rosario</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Serrano Vargas, Martina Rafaela</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vasquez Mendoza, Carlos Didier</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Villagrán Marchant, Diego Gabriel</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Zapata Urtasun, José Antonio</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1774,7 +2874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1983,7 +3083,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Muñoz Guajardo, Rosa Lucila del Carmen</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -2001,6 +3101,534 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Araya, Anahis Alexandra</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Atenas Vega, Renata Gabriela</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Burdiles Soto, Isidora del Pilar</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Calfuqueo Ortiz, Genesis Constanza</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cornejo Caro, Hilda Makarena</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Santelices, Constanza Javiera</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Gana Boggero, Dayma Antonella</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>García Gutiérrez, Benjamin Ignacio</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Jiménez Saavedra, Ainhoa Sarai</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Olea Guajardo, Milena Andrea</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Orfanoz Olmedo, Pascal Montserrat</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Pineda Hernández, Felipe Ignacio</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Ponce Soto, Vania Carolina</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Quezada Gatica, Pascal Francisca</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Quinzacara Aravena, Martina Fernanda</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Rivera Guerra, Martina Isidora</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rubilar Madariaga, Monserrat Ignacia</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Rubio Serrano, Javiera Antonia</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Santander Bugueño, Catalina Andrea</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Santis Alegría, Vicente Alejandro</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Aguilera, Giovanni Ignacio</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Zúñiga Fuenzalida, Maximiliano Joel</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -2494,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2703,7 +4331,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Mondaca Rivera, José Ignacio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -2721,6 +4349,556 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Herrera, Alexander Nathan</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Gatica, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alarcón Quispe, Sairi Catalina</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Bassaletti Barrera, Isabella Aurora</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Briones Alvarado, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cabra Jorquera, Martín José</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Canales Tamayo, Gustavo Esteban</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cruz Ortiz, Loreto Valentina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Del Canto Araya, Julieta</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Ebensperger Reyes, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fuenzalida García, Sofía</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Pavez, Martina Belén</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Hormilla Henríquez, Agustina Matilda Florencia Federica de La</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>López Cabello, Jenifer Antonia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>López Pérez, Maríajesús</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Mauricio Apaza, Ayde</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Molina Diaz, Natasha Gabriella</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Oliva González, Catalina Sofía</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Quinteros Román, Josefa Catalina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Reynals Gutiérrez, Julieta Antonia Antü</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Salazar Fredes, Leonardo</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sepúlveda Garrido, María Jesús Ignacia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Rodríguez, Lucas Octavio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Velasquez, Danny de Jesus</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -2974,7 +5152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2998,7 +5176,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: EG</t>
+          <t>Profesor: JM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3183,7 +5361,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Mondaca Rivera, José Ignacio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3201,6 +5379,556 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Herrera, Alexander Nathan</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Gatica, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alarcón Quispe, Sairi Catalina</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Bassaletti Barrera, Isabella Aurora</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Briones Alvarado, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cabra Jorquera, Martín José</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Canales Tamayo, Gustavo Esteban</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cruz Ortiz, Loreto Valentina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Del Canto Araya, Julieta</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Ebensperger Reyes, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fuenzalida García, Sofía</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Pavez, Martina Belén</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Hormilla Henríquez, Agustina Matilda Florencia Federica de La</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>López Cabello, Jenifer Antonia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>López Pérez, Maríajesús</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Mauricio Apaza, Ayde</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Molina Diaz, Natasha Gabriella</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Oliva González, Catalina Sofía</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Quinteros Román, Josefa Catalina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Reynals Gutiérrez, Julieta Antonia Antü</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Salazar Fredes, Leonardo</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sepúlveda Garrido, María Jesús Ignacia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Rodríguez, Lucas Octavio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Velasquez, Danny de Jesus</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -3478,7 +6206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3502,7 +6230,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: JM</t>
+          <t>Profesor: NV</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3687,7 +6415,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Riquelme Herrera, Alexander Nathan</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3706,6 +6434,556 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Varas Carrasco, Nathalie Gabriela</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Acuña Román, Crishna Alejandra</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Apablaza Maureira, Francisca Arelis</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Aravena Torres, Amanda Jesús</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Araya Peñafiel, Josefa Antonia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Arriagada Rivas, Noemí Yireh</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Coloma Canibilo, Carolina Ignacia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cuello Díaz, Francisco Alejandro</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Espinoza Godoy, Magdalena Constanza</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Flores Llanos, Catalina Andrea</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>González Bravo, Diego Pablo</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Peralta, Josepha Antonia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Herrera Mamani, Roberto Agustín</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Ibar Callejas, Bruno Gabriel</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Leviche Arteaga, Benjamin Alonso</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>López Navarro, Clara Agustina</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Manquel Contreras, Constanza Ignacia</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Mansilla Núñez, Muriel Stephania</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Méndez Molina, Josefa Valentina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Moya Cabello, Rocío Constanza</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rivera Abarca, Catalina Andrea</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Torres Meza, Javiera Alondra</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Valle Silva, Krishna Almendra</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Zurita Astorga, Byron Daniel Alfredo</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3718,7 +6996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3742,7 +7020,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: NV</t>
+          <t>Profesor: RM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3927,7 +7205,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Muñoz Guajardo, Rosa Lucila del Carmen</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -3945,6 +7223,556 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Herrera, Alexander Nathan</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Alcántar Correa, Fernanda Araceli</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alvarado Parada, Angel Ignacio</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Blanco Tamayo, Sebastián Alonso</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Chávez Álvarez, Lorenzo Andrés</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cofré Gatica, Martina Fernanda</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cordero Aravena, Tomás Esteban</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Flores Vergara, Andrés Argus Anthony</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Valderrama, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Lagos Herrera, Tathiana Isidora Aracelly</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Layseca Gallardo, Magdalena Francisca</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Morales Rojas, Maira Valentina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Morales Román, Gabriel Álvaro Max</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Olazabal Rosende, Sofía</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Peñaloza Muñoz, Camilo Ignacio</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Quilempan Díaz, Mainayen Amanda</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Serrano, Nehemìas David</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rubilar Paiva, Cyndell Jazmín</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sepúlveda Turra, Thais Pía</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Solari Gutiérrez, Giovanni Alonso</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Tolorza Orellana, Martina Augusta</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Uribe Paredes, Antonia Ignacia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vega Bilbao, Vicente Amaru</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Sánchez, Isidora Belén</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -4198,7 +8026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4407,7 +8235,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Guerra López, Eduardo Andrés</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -4426,6 +8254,512 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Alcalde Villegas, Victoria Camila</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Conejeros Monrroy, Diego Matías</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Labraña, Maite Cecilia</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Farías Púa, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Fuentes, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Romo, Magdalena Sofía</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Mateluna, Asiris Sayén</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Garrido Jara, Catalina Belén</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Kind Díaz, Luciano Andreas</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Landaeta Morales, Sofía Emilia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Lukaschewsky Cattoni, Baltazar</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Maragaño Arancibia, Catalina Paz</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Méndez Cuevas, Martín Ignacio</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Méndez González, Angelina Simone</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Nievas Orquera, Mia Catalina</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Oliva Martínez, Sofía Dominique</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Parada Álvarez, Josefa Paz</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Salinas Araneda, Alejandro Galahad</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sierpe Durán, Fernando Ramón</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Suárez Muñoz, Ítalo Alejandro</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Triviño Valladares, María Agustina</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Verdugo Marilaf, Ana Elisabet</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4438,7 +8772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4462,7 +8796,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: SM</t>
+          <t>Profesor: GF</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4647,7 +8981,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Fraczinet González, Gabriel Gastón</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -4666,6 +9000,512 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Aguilar Martínez, Javiera Elizabeth</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Besoain Acevedo, Matías André</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Castro Conejeros, Genesis Marcela</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Catalán Nicucheo, Felipe Arturo</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>González Santelices, Emilia Sofia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>González Sidgman, Isidora Catalina</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>González Valenzuela, Horacio</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Libbrecht Jequier, Martín</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Llantén Mardones, Sofía Paz</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>López Valle, Alannis Francis</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Martin González, Benjamín Andres</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Monzo Díaz, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Durán, Paulina Montserrat</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Núñez Allende, Javiera Isidora</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Crickmay, Micaela Isabel</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Prieto Contreras, Josefa Antonia</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Pereira, Fernanda Lissette</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Romo Quilodrán, Vicente Cristóbal Tomás</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Rumatz Jiménez, Barbara Paulina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Solar Aguayo, María Fernanda</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Vargas Millaquipai, Belén Alejandra</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Zaldívar Santelices, Santiago</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4678,7 +9518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4702,7 +9542,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: SM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4887,7 +9727,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Marconi Sandoval, Sebastián Patricio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -4906,6 +9746,534 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Abregu Pinedo, Masiel Yamile</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguilera Venegas, Fernanda Jesùs</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Cabello Pino, Vicente Felipe</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Correa Barrera, Cristal del Carmen</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Gavilán Contreras, Cristopher David</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Godoy Alcántara, Daniel Benjamín</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>González Aguilar, Fabiana Sofía</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Ibáñez Urquieta, Victoria Andrea</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Jeria Alvarado, Johan Josue</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Lobos Contreras, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Martinez Navarro, Camila Antonia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Montenegro Arévalo, Sofía Catalina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Morales, Daniella Anais</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Yáñez, Ximena Paz</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Ramos Ahumada, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Riffo Zúñiga, Sebastián Franco</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Ríos Arancibia, Mariano Andrés Nicolás</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Sáez, Scarlett Polette</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sáez Moreno, Meicy Francisca</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Silva Cuevas, Joaquín Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Torres Villarroel, Carlos Tomás Jesús</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vásquez Quevedo, Martina Alejandra</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vigas Fernández, Renato Ignacio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4918,7 +10286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4942,7 +10310,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: RM</t>
+          <t>Profesor: EG</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5127,7 +10495,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Guerra López, Eduardo Andrés</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -5146,6 +10514,512 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Alcalde Villegas, Victoria Camila</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Conejeros Monrroy, Diego Matías</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Labraña, Maite Cecilia</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Farías Púa, Valentina Ignacia</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Fuentes, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Figueroa Romo, Magdalena Sofía</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Mateluna, Asiris Sayén</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Garrido Jara, Catalina Belén</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Kind Díaz, Luciano Andreas</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Landaeta Morales, Sofía Emilia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Lukaschewsky Cattoni, Baltazar</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Maragaño Arancibia, Catalina Paz</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Méndez Cuevas, Martín Ignacio</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Méndez González, Angelina Simone</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Nievas Orquera, Mia Catalina</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Oliva Martínez, Sofía Dominique</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Parada Álvarez, Josefa Paz</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Salinas Araneda, Alejandro Galahad</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sierpe Durán, Fernando Ramón</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Suárez Muñoz, Ítalo Alejandro</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Triviño Valladares, María Agustina</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Verdugo Marilaf, Ana Elisabet</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5158,7 +11032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5182,7 +11056,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: SM</t>
+          <t>Profesor: GF</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5367,7 +11241,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Fraczinet González, Gabriel Gastón</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -5386,6 +11260,512 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Aguilar Martínez, Javiera Elizabeth</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Besoain Acevedo, Matías André</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Castro Conejeros, Genesis Marcela</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Catalán Nicucheo, Felipe Arturo</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>González Santelices, Emilia Sofia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>González Sidgman, Isidora Catalina</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>González Valenzuela, Horacio</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Libbrecht Jequier, Martín</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Llantén Mardones, Sofía Paz</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>López Valle, Alannis Francis</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Martin González, Benjamín Andres</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Monzo Díaz, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Durán, Paulina Montserrat</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Núñez Allende, Javiera Isidora</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Crickmay, Micaela Isabel</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Prieto Contreras, Josefa Antonia</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Pereira, Fernanda Lissette</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Romo Quilodrán, Vicente Cristóbal Tomás</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Rumatz Jiménez, Barbara Paulina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Solar Aguayo, María Fernanda</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Vargas Millaquipai, Belén Alejandra</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Zaldívar Santelices, Santiago</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5398,7 +11778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5422,7 +11802,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: SM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5607,7 +11987,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Marconi Sandoval, Sebastián Patricio</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -5626,6 +12006,534 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Abregu Pinedo, Masiel Yamile</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguilera Venegas, Fernanda Jesùs</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Cabello Pino, Vicente Felipe</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Correa Barrera, Cristal del Carmen</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Gavilán Contreras, Cristopher David</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Godoy Alcántara, Daniel Benjamín</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>González Aguilar, Fabiana Sofía</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Ibáñez Urquieta, Victoria Andrea</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Jeria Alvarado, Johan Josue</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Lobos Contreras, Valentina Antonia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Martinez Navarro, Camila Antonia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Montenegro Arévalo, Sofía Catalina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Morales, Daniella Anais</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Yáñez, Ximena Paz</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Ramos Ahumada, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Riffo Zúñiga, Sebastián Franco</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Ríos Arancibia, Mariano Andrés Nicolás</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Sáez, Scarlett Polette</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sáez Moreno, Meicy Francisca</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Silva Cuevas, Joaquín Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Torres Villarroel, Carlos Tomás Jesús</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vásquez Quevedo, Martina Alejandra</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Vigas Fernández, Renato Ignacio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5638,7 +12546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5869,7 +12777,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -5889,6 +12797,630 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Varas Carrasco, Nathalie Gabriela</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Pastén, Camila Noemí</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ahumada Miranda, Josefa Juanita</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Álvarez Reyes, Nicole Amapola</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Barra Carrasco, Franco Manuel</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Bien-Aime, Marie Esther Claude</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Campos Sandoval, Emilia Antonia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cofré Riquelme, Matías Alexander</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Salazar, Allison Valentina</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Espinoza Venegas, Daniel</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Estrada Duarte, Josefa Antonia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Flores Gallegos, Felipe Alexis</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Ita Ponte, Yurico María</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Muñoz, Meygan Alejandra</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Osses, Juan Pablo</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Méndez Orellana, Fernanda Estefanía</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Morales Sánchez, Constanza Alejandra</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Caroca, Catalina Almendra</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Peña Gamboa, María Ignacia</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Perez Fernandez, Diana Carolina</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Canales, Thomas</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Romero Suárez, Benjamín Alonso</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Ruz Escobar, Josefa Yanka Daniela</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Salazar Redlich, Felipe Javier Ignacio</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Valdés Ibarra, Angel Julián</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -6166,7 +13698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6397,7 +13929,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -6418,6 +13950,606 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mondaca Rivera, José Ignacio</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ahumada Figueroa, María Jesús</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Araya Correa, Fernanda Javiera</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Becerra Hernández, Iara Pazcale</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Campos Bascuñán, Macarena Constanza</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Campos Gómez, Ayleén Alexandra</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Coronado Valenzuela, Julieta Ignacia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Eriza Martínez, Domingo</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>González Aliste, Rafael Alonso</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>González Osorio, Julieta Antonia</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Jara Álvarez, Noelia Rocío</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Lillo Figueroa, Renato Benjamín</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>López Vicencio, Ailín Carolina</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Macías Rivero, Jacinta Alejandra</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Morales Riquelme, Isidora Ignacia</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Moreno Olave, Martina Magdalena</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Orellana González, Sebastián Martín</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Ortega Olivares, Alexandre José Duban</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Otárola Angel, Matías Ignacio</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Ramírez Molina, Martín Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Ríos López, Roberta Antonia</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sánchez Muñoz, Monserrat Antonella</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sandoval González, Gabriela Natalia</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Zuloaga Pintado, Ana Martha Nicole</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6430,7 +14562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6661,7 +14793,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Bernal Santibáñez, Maximiliano Adolfo</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -6682,6 +14814,606 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aguilar Astudillo, Amanda Ester</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Alfaro Sepúlveda, Michelle Beatriz</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Alvear Quilpatay, Francisca Belén</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Barraza Flores, Javiera Antonia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Carrasco Reinoso, Alonso Alejandro</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Carrillo Opazo, Paula Victoria</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Castro Sotomayor, Tabita Abigail</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Colil Celis, Emilia Astrid</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Cornejo González, Álvaro Cristóbal</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Marambio, María José del Carmen</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gabarroche Pavez, Jacqueline Michelle</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Leyton Berríos, Javiera Ariadna</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Luza Neira, Josefa Isidora</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Montiel González, Javiera Elsa Esperanza</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Castro, Ignacio Andrés</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Retamal Suárez, Matilda Isolina</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Ríos Arriagada, Chirzy</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Ortega, Rayen Alen</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Ruminaus Contreras, Renato Isaac</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Sepúlveda Vidal, Antonella Paz</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Tamblay Vega, Ana Constanza</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Ubeda Díaz, Mayra Ignacia</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Valdivia Urrutia, Sofía Mayeth</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6694,7 +15426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6925,7 +15657,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -6945,6 +15677,630 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Varas Carrasco, Nathalie Gabriela</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Pastén, Camila Noemí</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ahumada Miranda, Josefa Juanita</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Álvarez Reyes, Nicole Amapola</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Barra Carrasco, Franco Manuel</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Bien-Aime, Marie Esther Claude</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Campos Sandoval, Emilia Antonia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cofré Riquelme, Matías Alexander</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Salazar, Allison Valentina</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Espinoza Venegas, Daniel</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Estrada Duarte, Josefa Antonia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Flores Gallegos, Felipe Alexis</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Ita Ponte, Yurico María</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Muñoz, Meygan Alejandra</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Osses, Juan Pablo</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Méndez Orellana, Fernanda Estefanía</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Morales Sánchez, Constanza Alejandra</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Caroca, Catalina Almendra</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Peña Gamboa, María Ignacia</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Perez Fernandez, Diana Carolina</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rojas Canales, Thomas</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Romero Suárez, Benjamín Alonso</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Ruz Escobar, Josefa Yanka Daniela</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Salazar Redlich, Felipe Javier Ignacio</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Valdés Ibarra, Angel Julián</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -6983,7 +16339,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: GM</t>
+          <t>Profesor: EG</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7235,7 +16591,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: JCS</t>
+          <t>Profesor: GM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
